--- a/contact_forms/013_tree_removal_services_quote_request_form--contact_forms.xlsx
+++ b/contact_forms/013_tree_removal_services_quote_request_form--contact_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'tree_removal',_'value':_'tree_removal'}</t>
+          <t>tree_removal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'tree_removal', 'value': 'Tree Removal'}</t>
+          <t>Tree Removal</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tree_trimming',_'value':_'tree_trimming'}</t>
+          <t>tree_trimming</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'tree_trimming', 'value': 'Tree Trimming'}</t>
+          <t>Tree Trimming</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'tree_shaping',_'value':_'tree_shaping'}</t>
+          <t>tree_shaping</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'tree_shaping', 'value': 'Tree Shaping'}</t>
+          <t>Tree Shaping</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'tree_pruning',_'value':_'tree_pruning'}</t>
+          <t>tree_pruning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'tree_pruning', 'value': 'Tree Pruning'}</t>
+          <t>Tree Pruning</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'tree_thinning',_'value':_'tree_thinning'}</t>
+          <t>tree_thinning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'tree_thinning', 'value': 'Tree Thinning'}</t>
+          <t>Tree Thinning</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'tree_stabilization',_'value':_'tree_stabilization'}</t>
+          <t>tree_stabilization</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'tree_stabilization', 'value': 'Tree Stabilization'}</t>
+          <t>Tree Stabilization</t>
         </is>
       </c>
     </row>
